--- a/resources/tiktok-shop-affiliate/files/ttsa-basics-settled-commission-tracker.xlsx
+++ b/resources/tiktok-shop-affiliate/files/ttsa-basics-settled-commission-tracker.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,11 +58,6 @@
       <color rgb="000C2733"/>
       <sz val="12"/>
     </font>
-    <font>
-      <i val="1"/>
-      <color rgb="005A5A5A"/>
-    </font>
-    <font/>
   </fonts>
   <fills count="5">
     <fill>
@@ -113,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -153,8 +148,6 @@
     <xf numFmtId="4" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -520,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -565,7 +558,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
@@ -773,7 +765,6 @@
         <v/>
       </c>
     </row>
-    <row r="26"/>
     <row r="27">
       <c r="B27" s="13" t="inlineStr">
         <is>
@@ -796,7 +787,6 @@
         <v/>
       </c>
     </row>
-    <row r="29"/>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
@@ -811,7 +801,6 @@
         </is>
       </c>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
@@ -822,13 +811,9 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>ePORTS — your ecom source. eports.global</t>
-        </is>
-      </c>
-    </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" s="18" t="n"/>
+          <t>ePORTS — your ecom source (eports.global)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
